--- a/config/yunying/levelaward.xlsx
+++ b/config/yunying/levelaward.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="levelaward" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="levelaward" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Lv.5に到達</t>
+          <t>达到Lv.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Lv.10に到達</t>
+          <t>达到Lv.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Lv.15に到達</t>
+          <t>达到Lv.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Lv.20に到達</t>
+          <t>达到Lv.20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Lv.25に到達</t>
+          <t>达到Lv.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Lv.30に到達</t>
+          <t>达到Lv.30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>Lv.35に到達</t>
+          <t>Lv.35等级</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>Lv.40に到達</t>
+          <t>达到Lv.40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Lv.45に到達</t>
+          <t>达到Lv.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1623,545 +1623,514 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
+          <t>达到Lv.50</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>等級到達50級</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Reach Lv. 50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Đạt LV50</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>레벨 50 달성</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{gold=100000;rmb=140;13=25}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>Lv.55に到達</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>等級到達55級</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reach Lv.55</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Đạt LV55</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>레벨 55 달성</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{gold=110000;rmb=150;13=30}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>Lv.60に到達</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>等級到達60級</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Reach Lv.60</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Đạt LV60</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>레벨 60 달성</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{gold=120000;rmb=160;13=35}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>Lv.65に到達</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>等級到達65級</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Reach Lv.65</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Đạt LV65</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>레벨 65 달성</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{gold=130000;rmb=170;14=10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>Lv.70に到達</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>等級到達70級</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Reach Lv.70</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Đạt LV70</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>레벨 70 달성</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{21013=10;gold=140000;rmb=180;14=15}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>Lv.75に到達</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>等級到達75級</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Reach Lv.75</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Đạt LV75</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>레벨 75 달성</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{gold=150000;304=10;rmb=190;14=20}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>Lv.80に到達</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>等級到達80級</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Reach Lv.80</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Đạt LV80</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>레벨 80 달성</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{21030=10;gold=160000;rmb=200;14=25}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>Lv.20に到達</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>等級到達20級</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Reach Lv.20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Đạt LV20</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>레벨 20 달성</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{81=1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>Lv.30に到達</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>等級到達30級</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Reach Lv.30</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Đạt LV30</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>레벨 30 달성</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{82=1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
           <t>Lv.50に到達</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>等級到達50級</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Reach Lv. 50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Reach Lv.50</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Đạt LV50</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>레벨 50 달성</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>{gold=100000;rmb=140;13=25}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>Lv.55に到達</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>等級到達55級</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Reach Lv.55</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Đạt LV55</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>레벨 55 달성</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>{gold=110000;rmb=150;13=30}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Lv.60に到達</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>等級到達60級</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Reach Lv.60</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Đạt LV60</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>레벨 60 달성</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>{gold=120000;rmb=160;13=35}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>Lv.65に到達</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>等級到達65級</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Reach Lv.65</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Đạt LV65</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>레벨 65 달성</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>{gold=130000;rmb=170;14=10}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>Lv.70に到達</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>等級到達70級</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Reach Lv.70</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Đạt LV70</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>레벨 70 달성</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>{21013=10;gold=140000;rmb=180;14=15}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>Lv.75に到達</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>等級到達75級</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Reach Lv.75</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Đạt LV75</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>레벨 75 달성</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>{gold=150000;304=10;rmb=190;14=20}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>Lv.80に到達</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>等級到達80級</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Reach Lv.80</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Đạt LV80</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>레벨 80 달성</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{21030=10;gold=160000;rmb=200;14=25}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" s="1" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3002</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{83=1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>Lv.20に到達</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>等級到達20級</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Reach Lv.20</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Đạt LV20</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>레벨 20 달성</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{81=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3002</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{84=1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>Lv.30に到達</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>等級到達30級</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Reach Lv.30</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Đạt LV30</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>레벨 30 달성</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{82=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3002</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{85=1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>Lv.50に到達</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>等級到達50級</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Reach Lv.50</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Đạt LV50</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>레벨 50 달성</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{83=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3003</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>Lv.20に到達</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>等級到達20級</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Đạt LV20</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>레벨 20 달성</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{84=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3003</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>Lv.30に到達</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>等級到達30級</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Đạt LV30</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>레벨 30 달성</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>{85=1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3003</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>Lv.50に到達</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>等級到達50級</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Đạt LV50</t>
